--- a/Toronto_Bikeshare_Stations_latest.xlsx
+++ b/Toronto_Bikeshare_Stations_latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbyw\Documents\2026_winter\spatial_stats_4GA3\Final_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joycewu/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CFB9DA-2DEA-4DBE-A5D9-E6782B3BF4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F0912B-2702-FD4F-8E80-4B17DA6B608C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD2C2722-0E66-47DE-A52F-2251A36C0A25}"/>
+    <workbookView xWindow="9240" yWindow="860" windowWidth="30860" windowHeight="15740" xr2:uid="{FD2C2722-0E66-47DE-A52F-2251A36C0A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
   <si>
     <t>X</t>
   </si>
@@ -261,6 +261,66 @@
   </si>
   <si>
     <t>DUNDAS ST E / REGENT PARK BLVD</t>
+  </si>
+  <si>
+    <t>Yonge-Bay Corridor</t>
+  </si>
+  <si>
+    <t>Yonge-Eglinton</t>
+  </si>
+  <si>
+    <t>Adelaide St W / York St</t>
+  </si>
+  <si>
+    <t>University Ave / Pearl St</t>
+  </si>
+  <si>
+    <t>University Ave / King St W - SMART</t>
+  </si>
+  <si>
+    <t>King St W / University Ave</t>
+  </si>
+  <si>
+    <t>King St W / York St</t>
+  </si>
+  <si>
+    <t>King St W / York St (2)</t>
+  </si>
+  <si>
+    <t>King St W / Bay St (West Side)</t>
+  </si>
+  <si>
+    <t>King St W / Bay St (East Side)</t>
+  </si>
+  <si>
+    <t>York St / Wellington St W (2)</t>
+  </si>
+  <si>
+    <t>York St / Wellington St W (1)</t>
+  </si>
+  <si>
+    <t>Yonge St / Montgomery Ave - SMART</t>
+  </si>
+  <si>
+    <t>Yonge St / Orchard View Blvd</t>
+  </si>
+  <si>
+    <t>Eglinton Ave E / Redpath Ave</t>
+  </si>
+  <si>
+    <t>Lillian St / Soudan Ave - SMART</t>
+  </si>
+  <si>
+    <t>Hillsdale Ave W / Yonge St</t>
+  </si>
+  <si>
+    <t>Lascelles Blvd / Eglinton Ave W</t>
+  </si>
+  <si>
+    <t>Soudan Ave / Yonge St</t>
+  </si>
+  <si>
+    <t>Eglinton Ave W / Henning Ave SMART</t>
   </si>
 </sst>
 </file>
@@ -416,7 +476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +701,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCC66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E986"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF769E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,16 +857,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -842,7 +910,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -919,8 +987,24 @@
     <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -972,9 +1056,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF769E"/>
+      <color rgb="FFF3E986"/>
+      <color rgb="FFFF99CC"/>
       <color rgb="FFCC66FF"/>
       <color rgb="FFCC9900"/>
-      <color rgb="FFFF99CC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1305,18 +1391,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C89659D-35B3-4D5F-85D9-84267DD868C6}">
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1422,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>-79.375160399999999</v>
       </c>
@@ -1356,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>-79.375106799999998</v>
       </c>
@@ -1376,7 +1462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>-79.374227000000005</v>
       </c>
@@ -1396,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>-79.376276200000007</v>
       </c>
@@ -1416,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>-79.375365299999999</v>
       </c>
@@ -1436,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>-79.373305400000007</v>
       </c>
@@ -1456,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>-79.374217400000006</v>
       </c>
@@ -1476,7 +1562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>-79.376845900000006</v>
       </c>
@@ -1496,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>-79.378616199999996</v>
       </c>
@@ -1516,7 +1602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>-79.378744900000001</v>
       </c>
@@ -1536,7 +1622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>-79.376717200000002</v>
       </c>
@@ -1556,7 +1642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>-79.375064899999998</v>
       </c>
@@ -1576,7 +1662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>-79.376717200000002</v>
       </c>
@@ -1596,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>-79.380257700000001</v>
       </c>
@@ -1616,7 +1702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>-79.374808099999996</v>
       </c>
@@ -1636,7 +1722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>-79.377222099999997</v>
       </c>
@@ -1656,7 +1742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>-79.3785417</v>
       </c>
@@ -1676,7 +1762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>-79.379636099999999</v>
       </c>
@@ -1696,7 +1782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>-79.380708900000002</v>
       </c>
@@ -1716,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>-79.376900199999994</v>
       </c>
@@ -1736,7 +1822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>-79.379056700000007</v>
       </c>
@@ -1756,7 +1842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>-79.379046000000002</v>
       </c>
@@ -1776,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>-79.324089299999997</v>
       </c>
@@ -1796,7 +1882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>-79.316890299999997</v>
       </c>
@@ -1816,7 +1902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>-79.316106599999998</v>
       </c>
@@ -1836,7 +1922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>-79.311342999999994</v>
       </c>
@@ -1856,7 +1942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>-79.561869999999999</v>
       </c>
@@ -1876,7 +1962,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>-79.394260000000003</v>
       </c>
@@ -1896,7 +1982,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>-79.398960000000002</v>
       </c>
@@ -1916,7 +2002,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>-79.395740000000004</v>
       </c>
@@ -1936,7 +2022,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>-79.391379999999998</v>
       </c>
@@ -1956,7 +2042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>-79.349890000000002</v>
       </c>
@@ -1976,7 +2062,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>-79.345460000000003</v>
       </c>
@@ -1996,7 +2082,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>-79.343639999999994</v>
       </c>
@@ -2016,7 +2102,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>-79.348089999999999</v>
       </c>
@@ -2036,7 +2122,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>-79.341499999999996</v>
       </c>
@@ -2056,7 +2142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>-79.336870000000005</v>
       </c>
@@ -2076,7 +2162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
         <v>-79.333730000000003</v>
       </c>
@@ -2096,7 +2182,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>-79.334710000000001</v>
       </c>
@@ -2116,7 +2202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>-79.337850000000003</v>
       </c>
@@ -2136,7 +2222,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>-79.3352</v>
       </c>
@@ -2156,7 +2242,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="19">
         <v>-79.402839999999998</v>
       </c>
@@ -2176,7 +2262,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>-79.399339999999995</v>
       </c>
@@ -2196,7 +2282,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
         <v>-79.401840000000007</v>
       </c>
@@ -2216,7 +2302,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
         <v>-79.400049999999993</v>
       </c>
@@ -2236,7 +2322,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="19">
         <v>-79.398060000000001</v>
       </c>
@@ -2256,7 +2342,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="19">
         <v>-79.401380000000003</v>
       </c>
@@ -2276,7 +2362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="19">
         <v>-79.397829999999999</v>
       </c>
@@ -2296,7 +2382,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="19">
         <v>-79.397729999999996</v>
       </c>
@@ -2316,7 +2402,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="19">
         <v>-79.398039999999995</v>
       </c>
@@ -2336,7 +2422,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="19">
         <v>-79.397099999999995</v>
       </c>
@@ -2356,7 +2442,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="25">
         <v>-79.123207699999995</v>
       </c>
@@ -2376,7 +2462,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="25">
         <v>-79.130147300000004</v>
       </c>
@@ -2396,7 +2482,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="25">
         <v>-79.131917599999994</v>
       </c>
@@ -2416,7 +2502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="28">
         <v>-79.361520600000006</v>
       </c>
@@ -2436,7 +2522,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="28">
         <v>-79.362529600000002</v>
       </c>
@@ -2456,7 +2542,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="28">
         <v>-79.364095500000005</v>
       </c>
@@ -2476,7 +2562,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="28">
         <v>-79.365768700000004</v>
       </c>
@@ -2496,7 +2582,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="28">
         <v>-79.358046700000003</v>
       </c>
@@ -2516,7 +2602,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="28">
         <v>-79.358501799999999</v>
       </c>
@@ -2536,24 +2622,384 @@
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="31">
         <v>-79.361271400000007</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B62" s="28">
         <v>43.660216300000002</v>
       </c>
-      <c r="C62" s="32" t="s">
+      <c r="C62" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="30">
         <v>5</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="30">
         <v>72</v>
       </c>
-      <c r="F62" s="32" t="s">
+      <c r="F62" s="29" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="32">
+        <v>-79.383629999999997</v>
+      </c>
+      <c r="B63" s="34">
+        <v>43.649189999999997</v>
+      </c>
+      <c r="C63" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D63" s="38">
+        <v>9</v>
+      </c>
+      <c r="E63" s="38">
+        <v>5</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="32">
+        <v>-79.385350000000003</v>
+      </c>
+      <c r="B64" s="34">
+        <v>43.648359999999997</v>
+      </c>
+      <c r="C64" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" s="38">
+        <v>4</v>
+      </c>
+      <c r="E64" s="38">
+        <v>5</v>
+      </c>
+      <c r="F64" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="32">
+        <v>-79.384789999999995</v>
+      </c>
+      <c r="B65" s="34">
+        <v>43.647770000000001</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D65" s="38">
+        <v>21</v>
+      </c>
+      <c r="E65" s="38">
+        <v>5</v>
+      </c>
+      <c r="F65" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="32">
+        <v>-79.384280000000004</v>
+      </c>
+      <c r="B66" s="34">
+        <v>43.64781</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="38">
+        <v>29</v>
+      </c>
+      <c r="E66" s="38">
+        <v>5</v>
+      </c>
+      <c r="F66" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="32">
+        <v>-79.383170000000007</v>
+      </c>
+      <c r="B67" s="34">
+        <v>43.648000000000003</v>
+      </c>
+      <c r="C67" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" s="38">
+        <v>11</v>
+      </c>
+      <c r="E67" s="38">
+        <v>5</v>
+      </c>
+      <c r="F67" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="32">
+        <v>-79.383160000000004</v>
+      </c>
+      <c r="B68" s="34">
+        <v>43.647959999999998</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="38">
+        <v>15</v>
+      </c>
+      <c r="E68" s="38">
+        <v>5</v>
+      </c>
+      <c r="F68" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="32">
+        <v>-79.380570000000006</v>
+      </c>
+      <c r="B69" s="34">
+        <v>43.648519999999998</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="38">
+        <v>36</v>
+      </c>
+      <c r="E69" s="38">
+        <v>5</v>
+      </c>
+      <c r="F69" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="32">
+        <v>-79.380039999999994</v>
+      </c>
+      <c r="B70" s="34">
+        <v>43.648569999999999</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" s="38">
+        <v>4</v>
+      </c>
+      <c r="E70" s="38">
+        <v>5</v>
+      </c>
+      <c r="F70" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="32">
+        <v>-79.383139999999997</v>
+      </c>
+      <c r="B71" s="34">
+        <v>43.647039999999997</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" s="38">
+        <v>18</v>
+      </c>
+      <c r="E71" s="38">
+        <v>5</v>
+      </c>
+      <c r="F71" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="32">
+        <v>-79.383009999999999</v>
+      </c>
+      <c r="B72" s="34">
+        <v>43.646729999999998</v>
+      </c>
+      <c r="C72" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" s="38">
+        <v>16</v>
+      </c>
+      <c r="E72" s="38">
+        <v>5</v>
+      </c>
+      <c r="F72" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="33">
+        <v>-79.399150000000006</v>
+      </c>
+      <c r="B73" s="35">
+        <v>43.709600000000002</v>
+      </c>
+      <c r="C73" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D73" s="39">
+        <v>12</v>
+      </c>
+      <c r="E73" s="39">
+        <v>58</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="33">
+        <v>-79.398859999999999</v>
+      </c>
+      <c r="B74" s="35">
+        <v>43.708350000000003</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74" s="39">
+        <v>33</v>
+      </c>
+      <c r="E74" s="39">
+        <v>58</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="33">
+        <v>-79.401610000000005</v>
+      </c>
+      <c r="B75" s="35">
+        <v>43.706339999999997</v>
+      </c>
+      <c r="C75" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" s="39">
+        <v>19</v>
+      </c>
+      <c r="E75" s="39">
+        <v>58</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="33">
+        <v>-79.397279999999995</v>
+      </c>
+      <c r="B76" s="35">
+        <v>43.70431</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" s="39">
+        <v>18</v>
+      </c>
+      <c r="E76" s="39">
+        <v>58</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="33">
+        <v>-79.403549999999996</v>
+      </c>
+      <c r="B77" s="35">
+        <v>43.705469999999998</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="39">
+        <v>18</v>
+      </c>
+      <c r="E77" s="39">
+        <v>58</v>
+      </c>
+      <c r="F77" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="33">
+        <v>-79.397900000000007</v>
+      </c>
+      <c r="B78" s="35">
+        <v>43.702970000000001</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="39">
+        <v>14</v>
+      </c>
+      <c r="E78" s="39">
+        <v>58</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="33">
+        <v>-79.393559999999994</v>
+      </c>
+      <c r="B79" s="35">
+        <v>43.706069999999997</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D79" s="39">
+        <v>32</v>
+      </c>
+      <c r="E79" s="39">
+        <v>58</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="33">
+        <v>-79.392480000000006</v>
+      </c>
+      <c r="B80" s="35">
+        <v>43.707859999999997</v>
+      </c>
+      <c r="C80" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="39">
+        <v>31</v>
+      </c>
+      <c r="E80" s="39">
+        <v>58</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2564,11 +3010,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ccd10a38-0784-4501-a497-12b1af63237f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2793,27 +3240,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ccd10a38-0784-4501-a497-12b1af63237f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ABC736D-3725-4061-8E31-E72C6B38E3B4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B2EF9-D206-4606-8469-21E2C7BDAE17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="ccd10a38-0784-4501-a497-12b1af63237f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4ebc3a59-96f1-49e9-819a-e8e4fc8893ce"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2838,9 +3275,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B2EF9-D206-4606-8469-21E2C7BDAE17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ABC736D-3725-4061-8E31-E72C6B38E3B4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="ccd10a38-0784-4501-a497-12b1af63237f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4ebc3a59-96f1-49e9-819a-e8e4fc8893ce"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>